--- a/hall/resources/sample/MiniGameList.xlsx
+++ b/hall/resources/sample/MiniGameList.xlsx
@@ -703,7 +703,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -726,15 +726,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1115,11 +1106,11 @@
       <c r="A5" s="8">
         <v>1001</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="10">
-        <v>0</v>
+      <c r="C5" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1128,74 +1119,74 @@
       <c r="C6" s="8"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="8"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="8"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
       <c r="C9" s="8"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="10"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="10"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="11"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="11"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="11"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="11"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="11"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="11"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/MiniGameList.xlsx
+++ b/hall/resources/sample/MiniGameList.xlsx
@@ -1110,7 +1110,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
